--- a/hourly datasets/cap_gen_year15final.xlsx
+++ b/hourly datasets/cap_gen_year15final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1011243397437618</v>
+        <v>0.09984716858255856</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1059144125693297</v>
+        <v>0.1014121331244525</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2070387523130915</v>
+        <v>0.2012593017070111</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09557263292740131</v>
+        <v>0.08975440462309905</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1966969726711631</v>
+        <v>0.1896015732056576</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05574495268222329</v>
+        <v>0.043597188676648</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1568692924259851</v>
+        <v>0.1434443572592066</v>
       </c>
     </row>
     <row r="6">
@@ -549,15 +549,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04068131172004069</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>0.02568708135927368</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.001444460068946604</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.504645414426703</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01605110013487388</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0228480478819941</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02852611483655352</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.1418056514638025</v>
+        <v>0.1255342499418322</v>
       </c>
     </row>
     <row r="7">
@@ -567,15 +577,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02561311561565319</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>0.008841338025388026</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0005664404017622246</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.874497982338894</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.001737372992911669</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.007729566600522533</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.009953109450253886</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.126737455359415</v>
+        <v>0.1086885066079466</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +605,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03358538300629777</v>
+        <v>0.007413175805825335</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -593,7 +613,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1347097227500596</v>
+        <v>0.1072603443883839</v>
       </c>
     </row>
     <row r="9">
@@ -603,25 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03442816579262112</v>
+        <v>0.007244778353663894</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00141594982786167</v>
+        <v>0.0004562100550014009</v>
       </c>
       <c r="D9" t="n">
-        <v>6.537405176911589</v>
+        <v>1.703510567735875</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007345767487641948</v>
+        <v>0.002828416962293252</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03165177794909237</v>
+        <v>0.006349994869123615</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03720455363614848</v>
+        <v>0.008139561838203977</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1355525055363829</v>
+        <v>0.1070919469362225</v>
       </c>
     </row>
     <row r="10">
@@ -631,25 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0339338146056304</v>
+        <v>0.006454819063061809</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002175518972394081</v>
+        <v>0.001103723085180767</v>
       </c>
       <c r="D10" t="n">
-        <v>6.756659780268594</v>
+        <v>1.728911376123319</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006949519492414804</v>
+        <v>0.00486605003717258</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02966593777149067</v>
+        <v>0.004288243724612774</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03820169143977017</v>
+        <v>0.008621394401510662</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1350581543493922</v>
+        <v>0.1063019876456204</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0327383655909028</v>
+        <v>0.03113967874044345</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -667,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1338627053346646</v>
+        <v>0.130986847323002</v>
       </c>
     </row>
     <row r="12">
@@ -677,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05449241652816593</v>
+        <v>0.05145886855807805</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -685,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1556167562719277</v>
+        <v>0.1513060371406366</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06806478292631106</v>
+        <v>0.06529142187949739</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -703,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1691891226700729</v>
+        <v>0.165138590462056</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07758320361859486</v>
+        <v>0.07360028595564939</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -721,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1787075433623567</v>
+        <v>0.173447454538208</v>
       </c>
     </row>
     <row r="15">
@@ -731,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08353282968207291</v>
+        <v>0.07981643583114724</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -739,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1846571694258347</v>
+        <v>0.1796636044137058</v>
       </c>
     </row>
     <row r="16">
@@ -749,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08650998181587267</v>
+        <v>0.08248746614831091</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -757,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1876343215596345</v>
+        <v>0.1823346347308695</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08938267756420135</v>
+        <v>0.08583550138397902</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -775,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1905070173079632</v>
+        <v>0.1856826699665376</v>
       </c>
     </row>
     <row r="18">
@@ -785,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1011243397437618</v>
+        <v>-0.09984716858255856</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008565126237189784</v>
+        <v>0.008273659448641562</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.48051040529181</v>
+        <v>-18.56667711582888</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02666114851933578</v>
+        <v>0.02793031615414992</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1179468983065625</v>
+        <v>-0.116092722742011</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08430178118096128</v>
+        <v>-0.08360161442310637</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -813,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08808702858097425</v>
+        <v>0.08592399238094567</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -821,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1892113683247361</v>
+        <v>0.1857711609635042</v>
       </c>
     </row>
     <row r="20">
@@ -831,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09420210484596651</v>
+        <v>0.09095004292262587</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -839,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1953264445897283</v>
+        <v>0.1907972115051844</v>
       </c>
     </row>
     <row r="21">
@@ -849,25 +869,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09973090790117507</v>
+        <v>0.09572934420682262</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007179971999636597</v>
+        <v>0.006820569542769949</v>
       </c>
       <c r="D21" t="n">
-        <v>24.66851722583405</v>
+        <v>24.37599618999648</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04275798371787459</v>
+        <v>0.04275048698912935</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08562512037391359</v>
+        <v>0.08232988960342878</v>
       </c>
       <c r="G21" t="n">
-        <v>0.113836695428437</v>
+        <v>0.1091287988102168</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2008552476449369</v>
+        <v>0.1955765127893812</v>
       </c>
     </row>
     <row r="22">
@@ -877,25 +897,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1040090445197312</v>
+        <v>0.1002664317745428</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007280550556782495</v>
+        <v>0.007037685341265835</v>
       </c>
       <c r="D22" t="n">
-        <v>25.54785006092779</v>
+        <v>25.25852895373328</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03768649338384446</v>
+        <v>0.03659595219259526</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08969864624144257</v>
+        <v>0.08643328851192891</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1183194427980196</v>
+        <v>0.1140995750371563</v>
       </c>
       <c r="H22" t="n">
-        <v>0.205133384263493</v>
+        <v>0.2001136003571014</v>
       </c>
     </row>
     <row r="23">
@@ -905,25 +925,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1072261708738029</v>
+        <v>0.1032155863014072</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007381001408381161</v>
+        <v>0.007000759712132664</v>
       </c>
       <c r="D23" t="n">
-        <v>-438475234852.7534</v>
+        <v>-433380706051.431</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03799225941035007</v>
+        <v>0.03784290247689891</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09272396700087966</v>
+        <v>0.08946155314291412</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1217283747467261</v>
+        <v>0.1169696194599002</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2083505106175647</v>
+        <v>0.2030627548839658</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +953,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1116833987350626</v>
+        <v>0.1087012926725811</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007443584060648076</v>
+        <v>0.006989170161348098</v>
       </c>
       <c r="D24" t="n">
-        <v>26.84287002548955</v>
+        <v>26.81757501312093</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04165186913903106</v>
+        <v>0.03875596314647188</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09704931595348699</v>
+        <v>0.09496057683267084</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1263174815166377</v>
+        <v>0.1224420085124909</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2128077384788244</v>
+        <v>0.2085484612551396</v>
       </c>
     </row>
     <row r="25">
@@ -961,7 +981,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1114848809021334</v>
+        <v>0.1084962130772013</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -969,7 +989,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.2126092206458952</v>
+        <v>0.2083433816597599</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +999,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.114026800815633</v>
+        <v>0.1106854833545713</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007233691268618695</v>
+        <v>0.006949524990543517</v>
       </c>
       <c r="D26" t="n">
-        <v>236832989246.0349</v>
+        <v>234549857384.8951</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04945061947872778</v>
+        <v>0.04844421470255115</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09981357336792267</v>
+        <v>0.09702923369124528</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1282400282633437</v>
+        <v>0.1243417330178973</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2151511405593948</v>
+        <v>0.2105326519371299</v>
       </c>
     </row>
     <row r="27">
@@ -1007,7 +1027,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1151189497054282</v>
+        <v>0.1125341769067821</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1015,7 +1035,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.21624328944919</v>
+        <v>0.2123813454893406</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1158395932102434</v>
+        <v>0.1119604333313252</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006644235413936671</v>
+        <v>0.006369114855228905</v>
       </c>
       <c r="D28" t="n">
-        <v>26.21812983995269</v>
+        <v>26.29740101122929</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07409958591981149</v>
+        <v>0.07257620745488658</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1027944907970785</v>
+        <v>0.09945457646627698</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1288846956234086</v>
+        <v>0.1244662901963739</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2169639329540052</v>
+        <v>0.2118076019138838</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.03391983888776901</v>
+        <v>0.005924153146867669</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001755949212353712</v>
+        <v>0.0007273457979987301</v>
       </c>
       <c r="D29" t="n">
-        <v>7.118703821210458</v>
+        <v>1.553874432294454</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004684000656112387</v>
+        <v>0.003612839515630365</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03046947069317098</v>
+        <v>0.004496609514323969</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03737020708236766</v>
+        <v>0.007351696779411245</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1350441786315308</v>
+        <v>0.1057713217294262</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year15final.xlsx
+++ b/hourly datasets/cap_gen_year15final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2267460944359589</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09984716858255856</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1000623986144893</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1014121331244525</v>
+        <v>0.3876511875461599</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2012593017070111</v>
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2609674917246902</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08975440462309905</v>
+        <v>0.3857972948187597</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1896015732056576</v>
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.25911359899729</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.043597188676648</v>
+        <v>0.3752532259813924</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1434443572592066</v>
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2485695301599228</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +566,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02568708135927368</v>
+        <v>0.3730330808223916</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001444460068946604</v>
+        <v>0.002275935366147331</v>
       </c>
       <c r="D6" t="n">
-        <v>4.504645414426703</v>
+        <v>11.01080048839752</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01605110013487388</v>
+        <v>0.01674842355458631</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0228480478819941</v>
+        <v>0.03251582949318568</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02852611483655352</v>
+        <v>0.04146205944485566</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1255342499418322</v>
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2463493850009219</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +597,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008841338025388026</v>
+        <v>0.3688928407478625</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0005664404017622246</v>
+        <v>0.001338165180139535</v>
       </c>
       <c r="D7" t="n">
-        <v>2.874497982338894</v>
+        <v>11.81546091162223</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001737372992911669</v>
+        <v>0.001770385721186204</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007729566600522533</v>
+        <v>0.01476624168093143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009953109450253886</v>
+        <v>0.02002486333593405</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1086885066079466</v>
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2422091449263929</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007413175805825335</v>
+        <v>0.4823271875504385</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -613,7 +636,10 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1072603443883839</v>
+        <v>197</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3556434917289688</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007244778353663894</v>
+        <v>0.4855406968763491</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004562100550014009</v>
+        <v>0.003582021048542645</v>
       </c>
       <c r="D9" t="n">
-        <v>1.703510567735875</v>
+        <v>83.7050713919585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002828416962293252</v>
+        <v>0.0044295610836962</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006349994869123615</v>
+        <v>0.2416955270244747</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008139561838203977</v>
+        <v>0.2557394734195289</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1070919469362225</v>
+        <v>197</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3588570010548795</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.006454819063061809</v>
+        <v>0.4872764777513007</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001103723085180767</v>
+        <v>0.004608259257588534</v>
       </c>
       <c r="D10" t="n">
-        <v>1.728911376123319</v>
+        <v>85.85018486684174</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00486605003717258</v>
+        <v>0.007831916392000218</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004288243724612774</v>
+        <v>0.242898509288434</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008621394401510662</v>
+        <v>0.2609736809462975</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1063019876456204</v>
+        <v>197</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3605927819298311</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03113967874044345</v>
+        <v>0.2724611080563215</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.130986847323002</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1457774122348518</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05145886855807805</v>
+        <v>0.2988032160876734</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1513060371406366</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1721195202662038</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06529142187949739</v>
+        <v>0.3131525416345377</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.165138590462056</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1864688458130681</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07360028595564939</v>
+        <v>0.3234899616603456</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.173447454538208</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.196806265838876</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07981643583114724</v>
+        <v>0.3315869967380751</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1796636044137058</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2049033009166054</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08248746614831091</v>
+        <v>0.3348581616271477</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1823346347308695</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2081744658056781</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08583550138397902</v>
+        <v>0.3404649530128935</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1856826699665376</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2137812571914239</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09984716858255856</v>
+        <v>0.1266836958214696</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008273659448641562</v>
+        <v>0.008648241787554712</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.56667711582888</v>
+        <v>-19.39589279691888</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02793031615414992</v>
+        <v>0.02868540151644226</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.116092722742011</v>
+        <v>-0.1214788046370713</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08360161442310637</v>
+        <v>-0.08751804678622789</v>
       </c>
       <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08592399238094567</v>
+        <v>0.3420863688034026</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1857711609635042</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.215402672981933</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09095004292262587</v>
+        <v>0.3468112772138956</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1907972115051844</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.220127581392426</v>
       </c>
     </row>
     <row r="21">
@@ -869,25 +931,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09572934420682262</v>
+        <v>0.3506019520467275</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006820569542769949</v>
+        <v>0.006806386236684603</v>
       </c>
       <c r="D21" t="n">
-        <v>24.37599618999648</v>
+        <v>24.34686923767769</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04275048698912935</v>
+        <v>0.0427122686742457</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08232988960342878</v>
+        <v>0.08217281871989422</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1091287988102168</v>
+        <v>0.108915925752482</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1955765127893812</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2239182562252579</v>
       </c>
     </row>
     <row r="22">
@@ -897,25 +962,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1002664317745428</v>
+        <v>0.3566112523033357</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007037685341265835</v>
+        <v>0.007031465731726593</v>
       </c>
       <c r="D22" t="n">
-        <v>25.25852895373328</v>
+        <v>25.2367007189944</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03659595219259526</v>
+        <v>0.03656317510258437</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08643328851192891</v>
+        <v>0.08635461735564808</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1140995750371563</v>
+        <v>0.1139964643173154</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2001136003571014</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2299275564818661</v>
       </c>
     </row>
     <row r="23">
@@ -925,25 +993,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1032155863014072</v>
+        <v>0.3612852412056464</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007000759712132664</v>
+        <v>0.006995236856573747</v>
       </c>
       <c r="D23" t="n">
-        <v>-433380706051.431</v>
+        <v>-433268409809.0929</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03784290247689891</v>
+        <v>0.03780937300245068</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08946155314291412</v>
+        <v>0.0893784252669462</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1169696194599002</v>
+        <v>0.1168647956314566</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2030627548839658</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2346015453841767</v>
       </c>
     </row>
     <row r="24">
@@ -953,25 +1024,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1087012926725811</v>
+        <v>0.3675074434989368</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006989170161348098</v>
+        <v>0.006979944795784849</v>
       </c>
       <c r="D24" t="n">
-        <v>26.81757501312093</v>
+        <v>26.78311231151094</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03875596314647188</v>
+        <v>0.03872880399198617</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09496057683267084</v>
+        <v>0.09482517489637846</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1224420085124909</v>
+        <v>0.1222703438477313</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2085484612551396</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2408237476774671</v>
       </c>
     </row>
     <row r="25">
@@ -981,7 +1055,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1084962130772013</v>
+        <v>0.3702685933073868</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -989,7 +1063,10 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.2083433816597599</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2435848974859172</v>
       </c>
     </row>
     <row r="26">
@@ -999,25 +1076,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1106854833545713</v>
+        <v>0.3736117090126993</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006949524990543517</v>
+        <v>0.006895040644195181</v>
       </c>
       <c r="D26" t="n">
-        <v>234549857384.8951</v>
+        <v>234457527661.0164</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04844421470255115</v>
+        <v>0.04840294750522948</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09702923369124528</v>
+        <v>0.09649309153370859</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1243417330178973</v>
+        <v>0.1235909303069622</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2105326519371299</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2469280131912297</v>
       </c>
     </row>
     <row r="27">
@@ -1027,7 +1107,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1125341769067821</v>
+        <v>0.3796883634074758</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1035,7 +1115,10 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.2123813454893406</v>
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2530046675860061</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1119604333313252</v>
+        <v>0.3870222828329672</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006369114855228905</v>
+        <v>0.006457454421006682</v>
       </c>
       <c r="D28" t="n">
-        <v>26.29740101122929</v>
+        <v>26.58676743893674</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07257620745488658</v>
+        <v>0.07320311775960789</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09945457646627698</v>
+        <v>0.1006719296972636</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1244662901963739</v>
+        <v>0.1260303401100059</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2118076019138838</v>
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2603385870114976</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005924153146867669</v>
+        <v>0.3405753145137997</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0007273457979987301</v>
+        <v>0.001784089280601315</v>
       </c>
       <c r="D29" t="n">
-        <v>1.553874432294454</v>
+        <v>11.9953854176906</v>
       </c>
       <c r="E29" t="n">
-        <v>0.003612839515630365</v>
+        <v>0.00509316714708879</v>
       </c>
       <c r="F29" t="n">
-        <v>0.004496609514323969</v>
+        <v>0.0162280227721054</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007351696779411245</v>
+        <v>0.02322769648209771</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1057713217294262</v>
+        <v>154</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2138916186923301</v>
       </c>
     </row>
   </sheetData>
